--- a/data/trans_orig/IP07_C12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C12_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de cansancio para realizar lo que le gusta en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de haber estado demasiado cansado/a para disfrutar de las cosas que le gusta hacer, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,82 +833,82 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4872</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4565</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4470</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4250</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4133</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>483</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5119</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9425</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3614</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7671</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>14826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32379</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27455</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36139</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>25590</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21022</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28261</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>83,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>31664</t>
+          <t>26932</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>22665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35201</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>57254</t>
+          <t>59311</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51317</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61627</t>
+          <t>64303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5515</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4639</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4848</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4637</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6089</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>7139</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>8013</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7635</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6730</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2990</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11010</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23,07%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26214</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29788</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>21131</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16885</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25043</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>72,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29281</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>46604</t>
+          <t>48456</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39178</t>
+          <t>40993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51584</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4702</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4927</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1627</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5464</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20,26%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5882</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>40,43%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24385</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20038</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>26248</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>74,29%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>11939</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8667</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>13849</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>82,06%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>59,57%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25038</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26963</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32425</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40057</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2879,107 +2879,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2928</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>3193</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3323</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2992,107 +2992,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>999</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>5098</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5945</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>5149</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>5741</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>22616</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>13466</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>34567</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>34526</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>10861</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>55393</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>51,41%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>16,17%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>57983</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92721</t>
+          <t>47555</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>45799</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>33999</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>55046</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>65,98%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>48,98%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>79,3%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>32059</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>11447</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>55561</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>47,74%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>82,74%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46251</t>
+          <t>32511</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>25032</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54344</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,27 +3298,27 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43289</t>
+          <t>64101</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>102040</t>
+          <t>88236</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4993</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>349</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3922</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1574</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5093</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1661</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5491</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>14,26%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3982</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>4772</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>4202</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>6436</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>12589</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>7638</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>4298</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>21,39%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>21477</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>51132</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>44879</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>55599</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>75,88%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>24220</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>18797</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>28236</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>67,83%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>79,07%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>53180</t>
+          <t>26821</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>47489</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57771</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>77401</t>
+          <t>77952</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>69567</t>
+          <t>70221</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>84204</t>
+          <t>84930</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4243,107 +4243,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>897</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>4274</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>4393</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>4474</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>4208</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>8091</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>4032</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>14056</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>38,49%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>3590</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>7787</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>25,81%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>27533</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>21514</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>32003</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>75,39%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>87,63%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>26587</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>22390</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>28751</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>74,19%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>27244</t>
+          <t>29311</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>31215</t>
+          <t>31999</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>56845</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>46679</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>58478</t>
+          <t>62187</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>4905</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>4681</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>369</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>5609</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>11567</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>8181</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5123,22 +5123,22 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>46828</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>33664</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>62044</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>58709</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>120246</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>58,02%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>47229</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>34555</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>65645</t>
+          <t>46695</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>105937</t>
+          <t>83016</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>77486</t>
+          <t>67161</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>187516</t>
+          <t>102150</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>207444</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>191666</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>220904</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>78,24%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>72,29%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>141527</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>82290</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>165928</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>68,29%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>39,71%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>80,06%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>208850</t>
+          <t>150568</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>189830</t>
+          <t>139094</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>222427</t>
+          <t>160769</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>350377</t>
+          <t>358012</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>274651</t>
+          <t>338021</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>378955</t>
+          <t>374492</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>459214</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
